--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_1.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_1.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01664905928077678</v>
+        <v>0.005792185051408472</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008408531073609142</v>
+        <v>0.008397486670106638</v>
       </c>
       <c r="C2" t="n">
-        <v>6312978</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6312978</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>4597923</v>
+        <v>4958335</v>
       </c>
       <c r="L2" t="n">
-        <v>2717522</v>
+        <v>3151764</v>
       </c>
       <c r="M2" t="n">
-        <v>641873</v>
+        <v>789777</v>
       </c>
       <c r="N2" t="n">
-        <v>26019</v>
+        <v>36322</v>
       </c>
       <c r="O2" t="n">
-        <v>378349</v>
+        <v>441909</v>
       </c>
       <c r="P2" t="n">
-        <v>150572</v>
+        <v>168670</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999868273735046</v>
+        <v>0.9999869465827942</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9136114120483398</v>
+        <v>0.9804167151451111</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8033757209777832</v>
+        <v>0.9247650504112244</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7538870573043823</v>
+        <v>0.9253250956535339</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2414353042840958</v>
+        <v>0.336342841386795</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8034968972206116</v>
+        <v>0.9375926852226257</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8797354698181152</v>
+        <v>0.9854694604873657</v>
       </c>
       <c r="X2" t="n">
-        <v>6312978</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,22 +742,22 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>6312978</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>4825783</v>
+        <v>4859786</v>
       </c>
       <c r="AG2" t="n">
-        <v>2962430</v>
+        <v>2976396</v>
       </c>
       <c r="AH2" t="n">
-        <v>798977</v>
+        <v>800400</v>
       </c>
       <c r="AI2" t="n">
-        <v>58950</v>
+        <v>59079</v>
       </c>
       <c r="AJ2" t="n">
-        <v>458776</v>
+        <v>458892</v>
       </c>
       <c r="AK2" t="n">
         <v>180009</v>
@@ -766,19 +766,19 @@
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567543864250183</v>
+        <v>0.9567511677742004</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9111810326576233</v>
+        <v>0.9111562967300415</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8583831191062927</v>
+        <v>0.8583635687828064</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6629480123519897</v>
+        <v>0.6629523634910583</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9021487236022949</v>
+        <v>0.9021071791648865</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -786,88 +786,88 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.003767049889161395</v>
+        <v>0.001222381538289742</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002016202349440813</v>
+        <v>0.002012055206499525</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4597923</v>
+        <v>4958335</v>
       </c>
       <c r="E3" t="n">
-        <v>436806</v>
+        <v>114880</v>
       </c>
       <c r="F3" t="n">
-        <v>3452</v>
+        <v>739</v>
       </c>
       <c r="G3" t="n">
-        <v>490</v>
+        <v>117</v>
       </c>
       <c r="H3" t="n">
-        <v>189</v>
+        <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>10016539</v>
+        <v>10069537</v>
       </c>
       <c r="K3" t="n">
-        <v>10855935</v>
+        <v>11242851</v>
       </c>
       <c r="L3" t="n">
-        <v>12409176</v>
+        <v>12888651</v>
       </c>
       <c r="M3" t="n">
-        <v>15188701</v>
+        <v>15419109</v>
       </c>
       <c r="N3" t="n">
-        <v>16158846</v>
+        <v>16255142</v>
       </c>
       <c r="O3" t="n">
-        <v>15728286</v>
+        <v>15877617</v>
       </c>
       <c r="P3" t="n">
-        <v>16115753</v>
+        <v>16220250</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9124858379364014</v>
+        <v>0.9771834015846252</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8347948789596558</v>
+        <v>0.9635666608810425</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6891826391220093</v>
+        <v>0.8463513851165771</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2923319041728973</v>
+        <v>0.4072475433349609</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7436323761940002</v>
+        <v>0.8682434558868408</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7791041135787964</v>
+        <v>0.8727485537528992</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>4825783</v>
+        <v>4859786</v>
       </c>
       <c r="Z3" t="n">
-        <v>197772</v>
+        <v>198925</v>
       </c>
       <c r="AA3" t="n">
-        <v>8501</v>
+        <v>8538</v>
       </c>
       <c r="AB3" t="n">
-        <v>6767</v>
+        <v>6785</v>
       </c>
       <c r="AC3" t="n">
         <v>45</v>
@@ -876,43 +876,43 @@
         <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>10016622</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>11072575</v>
+        <v>11122210</v>
       </c>
       <c r="AG3" t="n">
-        <v>12785515</v>
+        <v>12854847</v>
       </c>
       <c r="AH3" t="n">
-        <v>15266430</v>
+        <v>15350773</v>
       </c>
       <c r="AI3" t="n">
-        <v>16210624</v>
+        <v>16296775</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15771054</v>
+        <v>15857234</v>
       </c>
       <c r="AK3" t="n">
-        <v>16123083</v>
+        <v>16209483</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9577060341835022</v>
+        <v>0.9577614665031433</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100281000137329</v>
+        <v>0.9099526405334473</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578660488128662</v>
+        <v>0.8577353358268738</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6623223423957825</v>
+        <v>0.662402331829071</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9017089605331421</v>
+        <v>0.9016109108924866</v>
       </c>
       <c r="AR3" t="n">
         <v>0.931419849395752</v>
@@ -920,88 +920,88 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04913435326820983</v>
+        <v>0.02794956514634886</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03183346841779339</v>
+        <v>0.03179976081728091</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>409214</v>
+        <v>89207</v>
       </c>
       <c r="E4" t="n">
-        <v>2717522</v>
+        <v>3151764</v>
       </c>
       <c r="F4" t="n">
-        <v>120723</v>
+        <v>29673</v>
       </c>
       <c r="G4" t="n">
-        <v>3878</v>
+        <v>259</v>
       </c>
       <c r="H4" t="n">
-        <v>3692</v>
+        <v>24</v>
       </c>
       <c r="I4" t="n">
-        <v>287</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
         <v>83</v>
       </c>
       <c r="K4" t="n">
-        <v>434767</v>
+        <v>99040</v>
       </c>
       <c r="L4" t="n">
-        <v>665107</v>
+        <v>256414</v>
       </c>
       <c r="M4" t="n">
-        <v>209545</v>
+        <v>63736</v>
       </c>
       <c r="N4" t="n">
-        <v>81749</v>
+        <v>71669</v>
       </c>
       <c r="O4" t="n">
-        <v>92529</v>
+        <v>29414</v>
       </c>
       <c r="P4" t="n">
-        <v>20584</v>
+        <v>2487</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999933838844299</v>
+        <v>0.9999935030937195</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9130483269691467</v>
+        <v>0.9787973761558533</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8187839984893799</v>
+        <v>0.9437671899795532</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7200842499732971</v>
+        <v>0.8840780854225159</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2644570171833038</v>
+        <v>0.3684146702289581</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7724063992500305</v>
+        <v>0.9015864729881287</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8263674974441528</v>
+        <v>0.9256901741027832</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>203648</v>
+        <v>205130</v>
       </c>
       <c r="Z4" t="n">
-        <v>2962430</v>
+        <v>2976396</v>
       </c>
       <c r="AA4" t="n">
-        <v>82563</v>
+        <v>82709</v>
       </c>
       <c r="AB4" t="n">
-        <v>5472</v>
+        <v>5496</v>
       </c>
       <c r="AC4" t="n">
         <v>1136</v>
@@ -1013,19 +1013,19 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>218127</v>
+        <v>219681</v>
       </c>
       <c r="AG4" t="n">
-        <v>288768</v>
+        <v>290218</v>
       </c>
       <c r="AH4" t="n">
-        <v>131816</v>
+        <v>132072</v>
       </c>
       <c r="AI4" t="n">
-        <v>29971</v>
+        <v>30036</v>
       </c>
       <c r="AJ4" t="n">
-        <v>49761</v>
+        <v>49797</v>
       </c>
       <c r="AK4" t="n">
         <v>13254</v>
@@ -1034,19 +1034,19 @@
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572299718856812</v>
+        <v>0.957256019115448</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106041789054871</v>
+        <v>0.910554051399231</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8581244349479675</v>
+        <v>0.8580493927001953</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6626349687576294</v>
+        <v>0.6626772284507751</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9019287824630737</v>
+        <v>0.9018589854240417</v>
       </c>
       <c r="AR4" t="n">
         <v>0.931419849395752</v>
@@ -1059,82 +1059,82 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>15697</v>
+        <v>7661</v>
       </c>
       <c r="E5" t="n">
-        <v>203958</v>
+        <v>117999</v>
       </c>
       <c r="F5" t="n">
-        <v>641873</v>
+        <v>789777</v>
       </c>
       <c r="G5" t="n">
-        <v>28350</v>
+        <v>16938</v>
       </c>
       <c r="H5" t="n">
-        <v>39544</v>
+        <v>760</v>
       </c>
       <c r="I5" t="n">
-        <v>1932</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>440975</v>
+        <v>115774</v>
       </c>
       <c r="L5" t="n">
-        <v>537795</v>
+        <v>119171</v>
       </c>
       <c r="M5" t="n">
-        <v>289481</v>
+        <v>143378</v>
       </c>
       <c r="N5" t="n">
-        <v>62986</v>
+        <v>52867</v>
       </c>
       <c r="O5" t="n">
-        <v>130436</v>
+        <v>67060</v>
       </c>
       <c r="P5" t="n">
-        <v>42691</v>
+        <v>24593</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999949336051941</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9463708996772766</v>
+        <v>0.986914336681366</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9263361096382141</v>
+        <v>0.9771208167076111</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9694404006004333</v>
+        <v>0.9873834252357483</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9911366701126099</v>
+        <v>0.9924137592315674</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9863459467887878</v>
+        <v>0.9941231608390808</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9961251616477966</v>
+        <v>0.9983503818511963</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>7991</v>
+        <v>8038</v>
       </c>
       <c r="Z5" t="n">
-        <v>84775</v>
+        <v>85058</v>
       </c>
       <c r="AA5" t="n">
-        <v>798977</v>
+        <v>800400</v>
       </c>
       <c r="AB5" t="n">
-        <v>9911</v>
+        <v>9927</v>
       </c>
       <c r="AC5" t="n">
-        <v>29067</v>
+        <v>29099</v>
       </c>
       <c r="AD5" t="n">
         <v>633</v>
@@ -1143,19 +1143,19 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>213115</v>
+        <v>214323</v>
       </c>
       <c r="AG5" t="n">
-        <v>292887</v>
+        <v>294539</v>
       </c>
       <c r="AH5" t="n">
-        <v>132377</v>
+        <v>132755</v>
       </c>
       <c r="AI5" t="n">
-        <v>30055</v>
+        <v>30110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>50009</v>
+        <v>50077</v>
       </c>
       <c r="AK5" t="n">
         <v>13254</v>
@@ -1164,47 +1164,47 @@
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735913872718811</v>
+        <v>0.9735621213912964</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643803238868713</v>
+        <v>0.964378833770752</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838212132453918</v>
+        <v>0.9838677644729614</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963241219520569</v>
+        <v>0.9963361620903015</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938902258872986</v>
+        <v>0.9939160346984863</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983766674995422</v>
+        <v>0.9983852505683899</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>9840</v>
+        <v>2169</v>
       </c>
       <c r="E6" t="n">
-        <v>18700</v>
+        <v>23518</v>
       </c>
       <c r="F6" t="n">
-        <v>24872</v>
+        <v>22487</v>
       </c>
       <c r="G6" t="n">
-        <v>26019</v>
+        <v>36322</v>
       </c>
       <c r="H6" t="n">
-        <v>8939</v>
+        <v>4509</v>
       </c>
       <c r="I6" t="n">
-        <v>633</v>
+        <v>184</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,19 +1224,19 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>6433</v>
+        <v>6458</v>
       </c>
       <c r="Z6" t="n">
-        <v>5328</v>
+        <v>5342</v>
       </c>
       <c r="AA6" t="n">
-        <v>10850</v>
+        <v>10862</v>
       </c>
       <c r="AB6" t="n">
-        <v>58950</v>
+        <v>59079</v>
       </c>
       <c r="AC6" t="n">
-        <v>6963</v>
+        <v>6967</v>
       </c>
       <c r="AD6" t="n">
         <v>481</v>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>5413</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>59262</v>
+        <v>10775</v>
       </c>
       <c r="G7" t="n">
-        <v>48009</v>
+        <v>54001</v>
       </c>
       <c r="H7" t="n">
-        <v>378349</v>
+        <v>441909</v>
       </c>
       <c r="I7" t="n">
-        <v>17696</v>
+        <v>2273</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1304,13 +1304,13 @@
         <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>29572</v>
+        <v>29633</v>
       </c>
       <c r="AB7" t="n">
-        <v>7556</v>
+        <v>7563</v>
       </c>
       <c r="AC7" t="n">
-        <v>458776</v>
+        <v>458892</v>
       </c>
       <c r="AD7" t="n">
         <v>12042</v>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>230</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>1236</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>1022</v>
+        <v>354</v>
       </c>
       <c r="H8" t="n">
-        <v>40165</v>
+        <v>24087</v>
       </c>
       <c r="I8" t="n">
-        <v>150572</v>
+        <v>168670</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
